--- a/artfynd/A 6640-2026 artfynd.xlsx
+++ b/artfynd/A 6640-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>81612510</v>
+        <v>129752236</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flatbergsvägen, syd Lisjön, Dlr</t>
+          <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>467952.3689147274</v>
+        <v>467811</v>
       </c>
       <c r="R2" t="n">
-        <v>6720303.822460112</v>
+        <v>6720445</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-01-05</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,27 +771,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>81612519</v>
+        <v>81612510</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,8 +811,16 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -842,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>467858.5446015606</v>
+        <v>467952</v>
       </c>
       <c r="R3" t="n">
-        <v>6720369.460695054</v>
+        <v>6720304</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +862,9 @@
           <t>2020-01-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-01-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,49 +892,36 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>81612505</v>
+        <v>81612519</v>
       </c>
       <c r="B4" t="n">
-        <v>77532</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -966,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>467803.7364664619</v>
+        <v>467859</v>
       </c>
       <c r="R4" t="n">
-        <v>6720453.896326076</v>
+        <v>6720369</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,19 +963,9 @@
           <t>2020-01-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-01-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129750630</v>
+        <v>129750618</v>
       </c>
       <c r="B5" t="n">
-        <v>79094</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,25 +1004,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1077,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>467887</v>
+        <v>467903</v>
       </c>
       <c r="R5" t="n">
-        <v>6720422</v>
+        <v>6720426</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1140,57 +1102,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129750756</v>
+        <v>129752200</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>SV Mockflån, Dlr</t>
+          <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468052</v>
+        <v>467892</v>
       </c>
       <c r="R6" t="n">
-        <v>6720168</v>
+        <v>6720343</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,44 +1170,53 @@
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-18</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129750627</v>
+        <v>129750596</v>
       </c>
       <c r="B7" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1285,10 +1247,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467915</v>
+        <v>467965</v>
       </c>
       <c r="R7" t="n">
-        <v>6720421</v>
+        <v>6720387</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1351,11 +1313,11 @@
         <v>129750603</v>
       </c>
       <c r="B8" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1449,14 +1411,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129750740</v>
+        <v>129750621</v>
       </c>
       <c r="B9" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1487,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468029</v>
+        <v>467903</v>
       </c>
       <c r="R9" t="n">
-        <v>6720175</v>
+        <v>6720410</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1550,14 +1512,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129750646</v>
+        <v>129750627</v>
       </c>
       <c r="B10" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1588,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467894</v>
+        <v>467915</v>
       </c>
       <c r="R10" t="n">
-        <v>6720452</v>
+        <v>6720421</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,14 +1613,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129750621</v>
+        <v>129750630</v>
       </c>
       <c r="B11" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1689,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>467903</v>
+        <v>467887</v>
       </c>
       <c r="R11" t="n">
-        <v>6720410</v>
+        <v>6720422</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1752,32 +1714,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129750702</v>
+        <v>129750646</v>
       </c>
       <c r="B12" t="n">
-        <v>79713</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1790,10 +1752,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>467825</v>
+        <v>467894</v>
       </c>
       <c r="R12" t="n">
-        <v>6720427</v>
+        <v>6720452</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1853,14 +1815,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129750684</v>
+        <v>129750669</v>
       </c>
       <c r="B13" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1891,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>467843</v>
+        <v>467852</v>
       </c>
       <c r="R13" t="n">
-        <v>6720456</v>
+        <v>6720466</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1954,14 +1916,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129750669</v>
+        <v>129750684</v>
       </c>
       <c r="B14" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1992,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>467852</v>
+        <v>467843</v>
       </c>
       <c r="R14" t="n">
-        <v>6720466</v>
+        <v>6720456</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2055,44 +2017,36 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129750618</v>
+        <v>129750695</v>
       </c>
       <c r="B15" t="n">
-        <v>91659</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2101,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>467903</v>
+        <v>467833</v>
       </c>
       <c r="R15" t="n">
-        <v>6720426</v>
+        <v>6720451</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2164,14 +2118,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129750596</v>
+        <v>129750733</v>
       </c>
       <c r="B16" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2202,10 +2156,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467965</v>
+        <v>468016</v>
       </c>
       <c r="R16" t="n">
-        <v>6720387</v>
+        <v>6720164</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2265,14 +2219,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129750749</v>
+        <v>129750740</v>
       </c>
       <c r="B17" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2303,10 +2257,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>468062</v>
+        <v>468029</v>
       </c>
       <c r="R17" t="n">
-        <v>6720169</v>
+        <v>6720175</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2366,14 +2320,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129750695</v>
+        <v>129750749</v>
       </c>
       <c r="B18" t="n">
-        <v>79094</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2404,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467833</v>
+        <v>468062</v>
       </c>
       <c r="R18" t="n">
-        <v>6720451</v>
+        <v>6720169</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2467,14 +2421,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129752229</v>
+        <v>129752221</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2496,19 +2450,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>467981</v>
+        <v>468036</v>
       </c>
       <c r="R19" t="n">
-        <v>6720386</v>
+        <v>6720382</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,7 +2491,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2550,12 +2501,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt på två tallstammar.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2583,32 +2529,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129752194</v>
+        <v>129752222</v>
       </c>
       <c r="B20" t="n">
-        <v>79714</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2618,10 +2564,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>467977</v>
+        <v>468086</v>
       </c>
       <c r="R20" t="n">
-        <v>6720284</v>
+        <v>6720216</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,7 +2599,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2663,7 +2609,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2690,14 +2636,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129752224</v>
+        <v>129752223</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2719,19 +2665,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>468042</v>
+        <v>468046</v>
       </c>
       <c r="R21" t="n">
-        <v>6720252</v>
+        <v>6720265</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2763,7 +2706,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2773,12 +2716,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt på tallstam.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2787,7 +2725,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2806,45 +2743,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129752200</v>
+        <v>129752224</v>
       </c>
       <c r="B22" t="n">
-        <v>91660</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>467892</v>
+        <v>468042</v>
       </c>
       <c r="R22" t="n">
-        <v>6720343</v>
+        <v>6720252</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2876,7 +2816,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2886,7 +2826,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2895,6 +2840,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2913,14 +2859,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129752226</v>
+        <v>129752225</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2948,10 +2894,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>467952</v>
+        <v>468006</v>
       </c>
       <c r="R23" t="n">
-        <v>6720305</v>
+        <v>6720236</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2983,7 +2929,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2993,7 +2939,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3020,14 +2966,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129752223</v>
+        <v>129752226</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3055,10 +3001,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>468046</v>
+        <v>467952</v>
       </c>
       <c r="R24" t="n">
-        <v>6720265</v>
+        <v>6720305</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3090,7 +3036,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3100,7 +3046,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3127,32 +3073,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129752206</v>
+        <v>129752227</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3162,10 +3108,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>467849</v>
+        <v>467837</v>
       </c>
       <c r="R25" t="n">
-        <v>6720443</v>
+        <v>6720410</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3197,7 +3143,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3207,7 +3153,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,7 +3162,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3235,45 +3180,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129752201</v>
+        <v>129752228</v>
       </c>
       <c r="B26" t="n">
-        <v>78853</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>467978</v>
+        <v>467951</v>
       </c>
       <c r="R26" t="n">
-        <v>6720284</v>
+        <v>6720376</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3305,7 +3253,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3315,7 +3263,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På tre tallar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,14 +3296,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129752222</v>
+        <v>129752229</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3372,16 +3325,19 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>468086</v>
+        <v>467981</v>
       </c>
       <c r="R27" t="n">
-        <v>6720216</v>
+        <v>6720386</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3413,7 +3369,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3423,7 +3379,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt på två tallstammar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3432,6 +3393,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3450,14 +3412,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129752227</v>
+        <v>129752230</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3485,10 +3447,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>467837</v>
+        <v>467998</v>
       </c>
       <c r="R28" t="n">
-        <v>6720410</v>
+        <v>6720390</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3520,7 +3482,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3530,7 +3492,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3557,45 +3519,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129752236</v>
+        <v>129752231</v>
       </c>
       <c r="B29" t="n">
-        <v>78761</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mockflån SV, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>467811</v>
+        <v>468028</v>
       </c>
       <c r="R29" t="n">
-        <v>6720445</v>
+        <v>6720390</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3627,7 +3592,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3637,7 +3602,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt på tallstam.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,48 +3635,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129752228</v>
+        <v>81612505</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>79351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mockflån SV, Dlr</t>
+          <t>Flatbergsvägen, syd Lisjön, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>467951</v>
+        <v>467804</v>
       </c>
       <c r="R30" t="n">
-        <v>6720376</v>
+        <v>6720454</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3733,27 +3711,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2020-01-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På tre tallar.</t>
+          <t>2020-01-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3769,22 +3732,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129752230</v>
+        <v>129750702</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,37 +3755,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mockflån SV, Dlr</t>
+          <t>SV Mockflån, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>467998</v>
+        <v>467825</v>
       </c>
       <c r="R31" t="n">
-        <v>6720390</v>
+        <v>6720427</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3849,49 +3815,40 @@
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-18</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:04</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129752225</v>
+        <v>129752194</v>
       </c>
       <c r="B32" t="n">
-        <v>79095</v>
+        <v>79946</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3899,21 +3856,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3923,10 +3880,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>468006</v>
+        <v>467977</v>
       </c>
       <c r="R32" t="n">
-        <v>6720236</v>
+        <v>6720284</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3958,7 +3915,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3968,7 +3925,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3992,6 +3949,453 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>101066303</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flatbergsvägen SV Mockflån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>467831</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6720229</v>
+      </c>
+      <c r="S33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>18:56</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Höna vid vägkant.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129750756</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SV Mockflån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>468052</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6720168</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129752206</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mockflån SV, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>467849</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6720443</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129752201</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mockflån SV, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>467978</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6720284</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6640-2026 artfynd.xlsx
+++ b/artfynd/A 6640-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752236</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -889,6 +899,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81612510</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81612519</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750618</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752200</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,6 +1337,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750596</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750603</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750621</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1610,6 +1655,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750627</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1711,6 +1761,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750630</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1812,6 +1867,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750646</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,6 +1973,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750669</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2014,6 +2079,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750684</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2115,6 +2185,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750695</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750733</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2317,6 +2397,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750740</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2418,6 +2503,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750749</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752221</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752222</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2740,6 +2840,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752223</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2856,6 +2961,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752224</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2963,6 +3073,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752225</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3070,6 +3185,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752226</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3177,6 +3297,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752227</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3293,6 +3418,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752228</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3409,6 +3539,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752229</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3516,6 +3651,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752230</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3632,6 +3772,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752231</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3741,6 +3886,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81612505</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3842,6 +3992,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750702</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3949,6 +4104,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752194</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4073,6 +4233,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101066303</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4180,6 +4345,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129750756</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4288,6 +4458,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752206</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4396,8 +4571,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129752201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>